--- a/ipa_timeplan_sheungtsunglam.xlsx
+++ b/ipa_timeplan_sheungtsunglam.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myoffice.accenture.com/personal/masa_lam_accenture_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masa.lam\0_ipa\equity-insight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="434" documentId="8_{52ABB401-E745-4758-BDD8-91D4082E9887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7714048-88EF-4009-A91A-E71DD05EDD95}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9E329F-FD1F-48D6-8D76-91F0E2C20A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{F000D33A-2255-403B-81DF-EEBC7025E60B}"/>
   </bookViews>
@@ -458,10 +458,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4125,7 +4121,9 @@
       <c r="AG35" s="8"/>
       <c r="AH35" s="8"/>
       <c r="AI35" s="8"/>
-      <c r="AJ35" s="8"/>
+      <c r="AJ35" s="15">
+        <v>1</v>
+      </c>
       <c r="AK35" s="8"/>
       <c r="AL35" s="8"/>
       <c r="AM35" s="8"/>
@@ -4314,13 +4312,27 @@
       <c r="AH37" s="8"/>
       <c r="AI37" s="8"/>
       <c r="AJ37" s="8"/>
-      <c r="AK37" s="8"/>
-      <c r="AL37" s="8"/>
-      <c r="AM37" s="8"/>
-      <c r="AN37" s="8"/>
-      <c r="AO37" s="8"/>
-      <c r="AP37" s="8"/>
-      <c r="AQ37" s="8"/>
+      <c r="AK37" s="15">
+        <v>1</v>
+      </c>
+      <c r="AL37" s="15">
+        <v>1</v>
+      </c>
+      <c r="AM37" s="15">
+        <v>1</v>
+      </c>
+      <c r="AN37" s="15">
+        <v>1</v>
+      </c>
+      <c r="AO37" s="15">
+        <v>1</v>
+      </c>
+      <c r="AP37" s="15">
+        <v>1</v>
+      </c>
+      <c r="AQ37" s="15">
+        <v>1</v>
+      </c>
       <c r="AR37" s="8"/>
       <c r="AS37" s="8"/>
       <c r="AT37" s="8"/>

--- a/ipa_timeplan_sheungtsunglam.xlsx
+++ b/ipa_timeplan_sheungtsunglam.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masa.lam\0_ipa\equity-insight\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE58333B-0B41-4DF8-8D69-2D60C73AC62E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-9470" yWindow="-21710" windowWidth="38620" windowHeight="21820" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="timeplan" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="timeplan" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -22,215 +27,197 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="60">
   <si>
-    <t xml:space="preserve">Day</t>
+    <t>Day</t>
   </si>
   <si>
-    <t xml:space="preserve">7. April 2026</t>
+    <t>7. April 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">8. April 2026</t>
+    <t>8. April 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">9. April 2026</t>
+    <t>9. April 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">10. April 2026</t>
+    <t>10. April 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">14. April 2026</t>
+    <t>14. April 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">15. April 2026</t>
+    <t>15. April 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">16. April 2026</t>
+    <t>16. April 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">17. April 2026</t>
+    <t>17. April 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">21. April 2026</t>
+    <t>21. April 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">22. April 2026</t>
+    <t>22. April 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Hour</t>
+    <t>Hour</t>
   </si>
   <si>
-    <t xml:space="preserve">#</t>
+    <t>#</t>
   </si>
   <si>
-    <t xml:space="preserve">Type</t>
+    <t>Type</t>
   </si>
   <si>
-    <t xml:space="preserve">Task / Activity</t>
+    <t>Task / Activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Create repository and setup code base (Planned)</t>
+    <t>Create repository and setup code base (Planned)</t>
   </si>
   <si>
-    <t xml:space="preserve">(Actual)</t>
+    <t>(Actual)</t>
   </si>
   <si>
-    <t xml:space="preserve">Setup</t>
+    <t>Setup</t>
   </si>
   <si>
-    <t xml:space="preserve">Start PostgreSQL in a Podman container and verify connection with Backend</t>
+    <t>Start PostgreSQL in a Podman container and verify connection with Backend</t>
   </si>
   <si>
-    <t xml:space="preserve">I</t>
+    <t>I</t>
   </si>
   <si>
-    <t xml:space="preserve">Inform</t>
+    <t>Inform</t>
   </si>
   <si>
-    <t xml:space="preserve">Start documenting "inform" section of IPERKA</t>
+    <t>Start documenting "inform" section of IPERKA</t>
   </si>
   <si>
-    <t xml:space="preserve">Create ERD, document the work so far and write journal</t>
+    <t>Create ERD, document the work so far and write journal</t>
   </si>
   <si>
-    <t xml:space="preserve">P</t>
+    <t>P</t>
   </si>
   <si>
-    <t xml:space="preserve">Plan</t>
+    <t>Plan</t>
   </si>
   <si>
-    <t xml:space="preserve">Create 2 mock-ups for the frontend UI design (figma)</t>
+    <t>Create 2 mock-ups for the frontend UI design (figma)</t>
   </si>
   <si>
-    <t xml:space="preserve">Draft frontend and backend application structure (figma)</t>
+    <t>Draft frontend and backend application structure (figma)</t>
   </si>
   <si>
-    <t xml:space="preserve">Have expert meeting and do analysis/reflection</t>
+    <t>Have expert meeting and do analysis/reflection</t>
   </si>
   <si>
-    <t xml:space="preserve">Document project requirements based on "inform" section</t>
+    <t>Document project requirements based on "inform" section</t>
   </si>
   <si>
-    <t xml:space="preserve">Document implementation concept based on application structure draft</t>
+    <t>Document implementation concept based on application structure draft</t>
   </si>
   <si>
-    <t xml:space="preserve">Write test concept based on implementation concept</t>
+    <t>Write test concept based on implementation concept</t>
   </si>
   <si>
-    <t xml:space="preserve">Document "plan" section and write journal</t>
+    <t>Document "plan" section and write journal</t>
   </si>
   <si>
-    <t xml:space="preserve">E</t>
+    <t>E</t>
   </si>
   <si>
-    <t xml:space="preserve">Decide</t>
+    <t>Decide</t>
   </si>
   <si>
-    <t xml:space="preserve">Document solution variants</t>
+    <t>Document solution variants</t>
   </si>
   <si>
-    <t xml:space="preserve">Compare solution variants based on a pros vs cons</t>
+    <t>Compare solution variants based on a pros vs cons</t>
   </si>
   <si>
-    <t xml:space="preserve">Write decision justifications</t>
+    <t>Write decision justifications</t>
   </si>
   <si>
-    <t xml:space="preserve">Document "decide" section and write journal</t>
+    <t>Document "decide" section and write journal</t>
   </si>
   <si>
-    <t xml:space="preserve">R</t>
+    <t>R</t>
   </si>
   <si>
-    <t xml:space="preserve">Realise</t>
+    <t>Realise</t>
   </si>
   <si>
-    <t xml:space="preserve">Implement backend entities and its relations</t>
+    <t>Implement backend entities and its relations</t>
   </si>
   <si>
-    <t xml:space="preserve">Implement backend CRUD operations</t>
+    <t>Implement backend CRUD operations</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify data retrieval from backend from frontend</t>
+    <t>Verify data retrieval from backend from frontend</t>
   </si>
   <si>
-    <t xml:space="preserve">Create frontend services</t>
+    <t>Create frontend services</t>
   </si>
   <si>
-    <t xml:space="preserve">Manually test endpoints and document problems</t>
+    <t>Manually test endpoints and document problems</t>
   </si>
   <si>
-    <t xml:space="preserve">Build frontend UI layout</t>
+    <t>Build frontend UI layout</t>
   </si>
   <si>
-    <t xml:space="preserve">Implement frontend functionalities</t>
+    <t>Implement frontend functionalities</t>
   </si>
   <si>
-    <t xml:space="preserve">C</t>
+    <t>C</t>
   </si>
   <si>
-    <t xml:space="preserve">Control</t>
+    <t>Control</t>
   </si>
   <si>
-    <t xml:space="preserve">Write frontend tests</t>
+    <t>Write frontend tests</t>
   </si>
   <si>
-    <t xml:space="preserve">Write backend tests</t>
+    <t>Write backend tests</t>
   </si>
   <si>
-    <t xml:space="preserve">R/C</t>
+    <t>R/C</t>
   </si>
   <si>
-    <t xml:space="preserve">Realise + Control</t>
+    <t>Realise + Control</t>
   </si>
   <si>
-    <t xml:space="preserve">Document "realisation" and "control" section</t>
+    <t>Document "realisation" and "control" section</t>
   </si>
   <si>
-    <t xml:space="preserve">A</t>
+    <t>A</t>
   </si>
   <si>
-    <t xml:space="preserve">Evaulate</t>
+    <t>Evaulate</t>
   </si>
   <si>
-    <t xml:space="preserve">Compare realisation against requirements</t>
+    <t>Compare realisation against requirements</t>
   </si>
   <si>
-    <t xml:space="preserve">Evaluate planned objectives against achieved objectives</t>
+    <t>Evaluate planned objectives against achieved objectives</t>
   </si>
   <si>
-    <t xml:space="preserve">Document "evaluation" section</t>
+    <t>Document "evaluation" section</t>
   </si>
   <si>
-    <t xml:space="preserve">Finalise and hand in project</t>
+    <t>Finalise and hand in project</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="14"/>
@@ -240,7 +227,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
@@ -248,7 +235,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -296,7 +283,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.0998"/>
+        <fgColor theme="3" tint="9.9795525986510814E-2"/>
         <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
@@ -308,155 +295,112 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.5"/>
+        <fgColor theme="5" tint="-0.499984740745262"/>
         <bgColor rgb="FF993366"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="5">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="medium"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -515,60 +459,76 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF2F5496"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0e2841"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e8e8e8"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="e97132"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196b24"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0f9ed5"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="a02b93"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4ea72e"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607d"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -600,7 +560,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -624,7 +584,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -684,480 +644,479 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CE83"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="18.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="94.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="83" min="4" style="1" width="4.71"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="84" style="1" width="9.14"/>
+    <col min="1" max="1" width="13" style="3" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="94.28515625" style="3" customWidth="1"/>
+    <col min="4" max="83" width="4.7109375" style="3" customWidth="1"/>
+    <col min="84" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C1" s="2" t="s">
+    <row r="1" spans="1:83" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3" t="s">
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3" t="s">
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="3"/>
-      <c r="AB1" s="3" t="s">
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="AC1" s="3"/>
-      <c r="AD1" s="3"/>
-      <c r="AE1" s="3"/>
-      <c r="AF1" s="3"/>
-      <c r="AG1" s="3"/>
-      <c r="AH1" s="3"/>
-      <c r="AI1" s="3"/>
-      <c r="AJ1" s="3" t="s">
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="2"/>
+      <c r="AE1" s="2"/>
+      <c r="AF1" s="2"/>
+      <c r="AG1" s="2"/>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="AK1" s="3"/>
-      <c r="AL1" s="3"/>
-      <c r="AM1" s="3"/>
-      <c r="AN1" s="3"/>
-      <c r="AO1" s="3"/>
-      <c r="AP1" s="3"/>
-      <c r="AQ1" s="3"/>
-      <c r="AR1" s="3" t="s">
+      <c r="AK1" s="2"/>
+      <c r="AL1" s="2"/>
+      <c r="AM1" s="2"/>
+      <c r="AN1" s="2"/>
+      <c r="AO1" s="2"/>
+      <c r="AP1" s="2"/>
+      <c r="AQ1" s="2"/>
+      <c r="AR1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AS1" s="3"/>
-      <c r="AT1" s="3"/>
-      <c r="AU1" s="3"/>
-      <c r="AV1" s="3"/>
-      <c r="AW1" s="3"/>
-      <c r="AX1" s="3"/>
-      <c r="AY1" s="3"/>
-      <c r="AZ1" s="3" t="s">
+      <c r="AS1" s="2"/>
+      <c r="AT1" s="2"/>
+      <c r="AU1" s="2"/>
+      <c r="AV1" s="2"/>
+      <c r="AW1" s="2"/>
+      <c r="AX1" s="2"/>
+      <c r="AY1" s="2"/>
+      <c r="AZ1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="BA1" s="3"/>
-      <c r="BB1" s="3"/>
-      <c r="BC1" s="3"/>
-      <c r="BD1" s="3"/>
-      <c r="BE1" s="3"/>
-      <c r="BF1" s="3"/>
-      <c r="BG1" s="3"/>
-      <c r="BH1" s="3" t="s">
+      <c r="BA1" s="2"/>
+      <c r="BB1" s="2"/>
+      <c r="BC1" s="2"/>
+      <c r="BD1" s="2"/>
+      <c r="BE1" s="2"/>
+      <c r="BF1" s="2"/>
+      <c r="BG1" s="2"/>
+      <c r="BH1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="BI1" s="3"/>
-      <c r="BJ1" s="3"/>
-      <c r="BK1" s="3"/>
-      <c r="BL1" s="3"/>
-      <c r="BM1" s="3"/>
-      <c r="BN1" s="3"/>
-      <c r="BO1" s="3"/>
-      <c r="BP1" s="3" t="s">
+      <c r="BI1" s="2"/>
+      <c r="BJ1" s="2"/>
+      <c r="BK1" s="2"/>
+      <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
+      <c r="BN1" s="2"/>
+      <c r="BO1" s="2"/>
+      <c r="BP1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="BQ1" s="3"/>
-      <c r="BR1" s="3"/>
-      <c r="BS1" s="3"/>
-      <c r="BT1" s="3"/>
-      <c r="BU1" s="3"/>
-      <c r="BV1" s="3"/>
-      <c r="BW1" s="3"/>
-      <c r="BX1" s="3" t="s">
+      <c r="BQ1" s="2"/>
+      <c r="BR1" s="2"/>
+      <c r="BS1" s="2"/>
+      <c r="BT1" s="2"/>
+      <c r="BU1" s="2"/>
+      <c r="BV1" s="2"/>
+      <c r="BW1" s="2"/>
+      <c r="BX1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="BY1" s="3"/>
-      <c r="BZ1" s="3"/>
-      <c r="CA1" s="3"/>
-      <c r="CB1" s="3"/>
-      <c r="CC1" s="3"/>
-      <c r="CD1" s="3"/>
-      <c r="CE1" s="3"/>
+      <c r="BY1" s="2"/>
+      <c r="BZ1" s="2"/>
+      <c r="CA1" s="2"/>
+      <c r="CB1" s="2"/>
+      <c r="CC1" s="2"/>
+      <c r="CD1" s="2"/>
+      <c r="CE1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C2" s="4" t="s">
+    <row r="2" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4" t="n">
+      <c r="D2" s="5">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5">
         <v>2</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="5">
         <v>3</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="5">
         <v>4</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="5">
         <v>5</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="5">
         <v>6</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="J2" s="5">
         <v>7</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="K2" s="5">
         <v>8</v>
       </c>
-      <c r="L2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="4" t="n">
+      <c r="L2" s="5">
+        <v>1</v>
+      </c>
+      <c r="M2" s="5">
         <v>2</v>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="N2" s="5">
         <v>3</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="O2" s="5">
         <v>4</v>
       </c>
-      <c r="P2" s="4" t="n">
+      <c r="P2" s="5">
         <v>5</v>
       </c>
-      <c r="Q2" s="4" t="n">
+      <c r="Q2" s="5">
         <v>6</v>
       </c>
-      <c r="R2" s="4" t="n">
+      <c r="R2" s="5">
         <v>7</v>
       </c>
-      <c r="S2" s="4" t="n">
+      <c r="S2" s="5">
         <v>8</v>
       </c>
-      <c r="T2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" s="4" t="n">
+      <c r="T2" s="5">
+        <v>1</v>
+      </c>
+      <c r="U2" s="5">
         <v>2</v>
       </c>
-      <c r="V2" s="4" t="n">
+      <c r="V2" s="5">
         <v>3</v>
       </c>
-      <c r="W2" s="4" t="n">
+      <c r="W2" s="5">
         <v>4</v>
       </c>
-      <c r="X2" s="4" t="n">
+      <c r="X2" s="5">
         <v>5</v>
       </c>
-      <c r="Y2" s="4" t="n">
+      <c r="Y2" s="5">
         <v>6</v>
       </c>
-      <c r="Z2" s="4" t="n">
+      <c r="Z2" s="5">
         <v>7</v>
       </c>
-      <c r="AA2" s="4" t="n">
+      <c r="AA2" s="5">
         <v>8</v>
       </c>
-      <c r="AB2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="4" t="n">
+      <c r="AB2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="5">
         <v>2</v>
       </c>
-      <c r="AD2" s="4" t="n">
+      <c r="AD2" s="5">
         <v>3</v>
       </c>
-      <c r="AE2" s="4" t="n">
+      <c r="AE2" s="5">
         <v>4</v>
       </c>
-      <c r="AF2" s="4" t="n">
+      <c r="AF2" s="5">
         <v>5</v>
       </c>
-      <c r="AG2" s="4" t="n">
+      <c r="AG2" s="5">
         <v>6</v>
       </c>
-      <c r="AH2" s="4" t="n">
+      <c r="AH2" s="5">
         <v>7</v>
       </c>
-      <c r="AI2" s="4" t="n">
+      <c r="AI2" s="5">
         <v>8</v>
       </c>
-      <c r="AJ2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK2" s="4" t="n">
+      <c r="AJ2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AK2" s="5">
         <v>2</v>
       </c>
-      <c r="AL2" s="4" t="n">
+      <c r="AL2" s="5">
         <v>3</v>
       </c>
-      <c r="AM2" s="4" t="n">
+      <c r="AM2" s="5">
         <v>4</v>
       </c>
-      <c r="AN2" s="4" t="n">
+      <c r="AN2" s="5">
         <v>5</v>
       </c>
-      <c r="AO2" s="4" t="n">
+      <c r="AO2" s="5">
         <v>6</v>
       </c>
-      <c r="AP2" s="4" t="n">
+      <c r="AP2" s="5">
         <v>7</v>
       </c>
-      <c r="AQ2" s="4" t="n">
+      <c r="AQ2" s="5">
         <v>8</v>
       </c>
-      <c r="AR2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS2" s="4" t="n">
+      <c r="AR2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AS2" s="5">
         <v>2</v>
       </c>
-      <c r="AT2" s="4" t="n">
+      <c r="AT2" s="5">
         <v>3</v>
       </c>
-      <c r="AU2" s="4" t="n">
+      <c r="AU2" s="5">
         <v>4</v>
       </c>
-      <c r="AV2" s="4" t="n">
+      <c r="AV2" s="5">
         <v>5</v>
       </c>
-      <c r="AW2" s="4" t="n">
+      <c r="AW2" s="5">
         <v>6</v>
       </c>
-      <c r="AX2" s="4" t="n">
+      <c r="AX2" s="5">
         <v>7</v>
       </c>
-      <c r="AY2" s="4" t="n">
+      <c r="AY2" s="5">
         <v>8</v>
       </c>
-      <c r="AZ2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA2" s="4" t="n">
+      <c r="AZ2" s="5">
+        <v>1</v>
+      </c>
+      <c r="BA2" s="5">
         <v>2</v>
       </c>
-      <c r="BB2" s="4" t="n">
+      <c r="BB2" s="5">
         <v>3</v>
       </c>
-      <c r="BC2" s="4" t="n">
+      <c r="BC2" s="5">
         <v>4</v>
       </c>
-      <c r="BD2" s="4" t="n">
+      <c r="BD2" s="5">
         <v>5</v>
       </c>
-      <c r="BE2" s="4" t="n">
+      <c r="BE2" s="5">
         <v>6</v>
       </c>
-      <c r="BF2" s="4" t="n">
+      <c r="BF2" s="5">
         <v>7</v>
       </c>
-      <c r="BG2" s="4" t="n">
+      <c r="BG2" s="5">
         <v>8</v>
       </c>
-      <c r="BH2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI2" s="4" t="n">
+      <c r="BH2" s="5">
+        <v>1</v>
+      </c>
+      <c r="BI2" s="5">
         <v>2</v>
       </c>
-      <c r="BJ2" s="4" t="n">
+      <c r="BJ2" s="5">
         <v>3</v>
       </c>
-      <c r="BK2" s="4" t="n">
+      <c r="BK2" s="5">
         <v>4</v>
       </c>
-      <c r="BL2" s="4" t="n">
+      <c r="BL2" s="5">
         <v>5</v>
       </c>
-      <c r="BM2" s="4" t="n">
+      <c r="BM2" s="5">
         <v>6</v>
       </c>
-      <c r="BN2" s="4" t="n">
+      <c r="BN2" s="5">
         <v>7</v>
       </c>
-      <c r="BO2" s="4" t="n">
+      <c r="BO2" s="5">
         <v>8</v>
       </c>
-      <c r="BP2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ2" s="4" t="n">
+      <c r="BP2" s="5">
+        <v>1</v>
+      </c>
+      <c r="BQ2" s="5">
         <v>2</v>
       </c>
-      <c r="BR2" s="4" t="n">
+      <c r="BR2" s="5">
         <v>3</v>
       </c>
-      <c r="BS2" s="4" t="n">
+      <c r="BS2" s="5">
         <v>4</v>
       </c>
-      <c r="BT2" s="4" t="n">
+      <c r="BT2" s="5">
         <v>5</v>
       </c>
-      <c r="BU2" s="4" t="n">
+      <c r="BU2" s="5">
         <v>6</v>
       </c>
-      <c r="BV2" s="4" t="n">
+      <c r="BV2" s="5">
         <v>7</v>
       </c>
-      <c r="BW2" s="4" t="n">
+      <c r="BW2" s="5">
         <v>8</v>
       </c>
-      <c r="BX2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY2" s="4" t="n">
+      <c r="BX2" s="5">
+        <v>1</v>
+      </c>
+      <c r="BY2" s="5">
         <v>2</v>
       </c>
-      <c r="BZ2" s="4" t="n">
+      <c r="BZ2" s="5">
         <v>3</v>
       </c>
-      <c r="CA2" s="4" t="n">
+      <c r="CA2" s="5">
         <v>4</v>
       </c>
-      <c r="CB2" s="4" t="n">
+      <c r="CB2" s="5">
         <v>5</v>
       </c>
-      <c r="CC2" s="4" t="n">
+      <c r="CC2" s="5">
         <v>6</v>
       </c>
-      <c r="CD2" s="4" t="n">
+      <c r="CD2" s="5">
         <v>7</v>
       </c>
-      <c r="CE2" s="4" t="n">
+      <c r="CE2" s="5">
         <v>8</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:83" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="7"/>
-      <c r="AC3" s="7"/>
-      <c r="AD3" s="7"/>
-      <c r="AE3" s="7"/>
-      <c r="AF3" s="7"/>
-      <c r="AG3" s="7"/>
-      <c r="AH3" s="7"/>
-      <c r="AI3" s="7"/>
-      <c r="AJ3" s="7"/>
-      <c r="AK3" s="7"/>
-      <c r="AL3" s="7"/>
-      <c r="AM3" s="7"/>
-      <c r="AN3" s="7"/>
-      <c r="AO3" s="7"/>
-      <c r="AP3" s="7"/>
-      <c r="AQ3" s="7"/>
-      <c r="AR3" s="7"/>
-      <c r="AS3" s="7"/>
-      <c r="AT3" s="7"/>
-      <c r="AU3" s="7"/>
-      <c r="AV3" s="7"/>
-      <c r="AW3" s="7"/>
-      <c r="AX3" s="7"/>
-      <c r="AY3" s="7"/>
-      <c r="AZ3" s="7"/>
-      <c r="BA3" s="7"/>
-      <c r="BB3" s="7"/>
-      <c r="BC3" s="7"/>
-      <c r="BD3" s="7"/>
-      <c r="BE3" s="7"/>
-      <c r="BF3" s="7"/>
-      <c r="BG3" s="7"/>
-      <c r="BH3" s="7"/>
-      <c r="BI3" s="7"/>
-      <c r="BJ3" s="7"/>
-      <c r="BK3" s="7"/>
-      <c r="BL3" s="7"/>
-      <c r="BM3" s="7"/>
-      <c r="BN3" s="7"/>
-      <c r="BO3" s="7"/>
-      <c r="BP3" s="7"/>
-      <c r="BQ3" s="7"/>
-      <c r="BR3" s="7"/>
-      <c r="BS3" s="7"/>
-      <c r="BT3" s="7"/>
-      <c r="BU3" s="7"/>
-      <c r="BV3" s="7"/>
-      <c r="BW3" s="7"/>
-      <c r="BX3" s="7"/>
-      <c r="BY3" s="7"/>
-      <c r="BZ3" s="7"/>
-      <c r="CA3" s="7"/>
-      <c r="CB3" s="7"/>
-      <c r="CC3" s="7"/>
-      <c r="CD3" s="7"/>
-      <c r="CE3" s="7"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
+      <c r="AH3" s="1"/>
+      <c r="AI3" s="1"/>
+      <c r="AJ3" s="1"/>
+      <c r="AK3" s="1"/>
+      <c r="AL3" s="1"/>
+      <c r="AM3" s="1"/>
+      <c r="AN3" s="1"/>
+      <c r="AO3" s="1"/>
+      <c r="AP3" s="1"/>
+      <c r="AQ3" s="1"/>
+      <c r="AR3" s="1"/>
+      <c r="AS3" s="1"/>
+      <c r="AT3" s="1"/>
+      <c r="AU3" s="1"/>
+      <c r="AV3" s="1"/>
+      <c r="AW3" s="1"/>
+      <c r="AX3" s="1"/>
+      <c r="AY3" s="1"/>
+      <c r="AZ3" s="1"/>
+      <c r="BA3" s="1"/>
+      <c r="BB3" s="1"/>
+      <c r="BC3" s="1"/>
+      <c r="BD3" s="1"/>
+      <c r="BE3" s="1"/>
+      <c r="BF3" s="1"/>
+      <c r="BG3" s="1"/>
+      <c r="BH3" s="1"/>
+      <c r="BI3" s="1"/>
+      <c r="BJ3" s="1"/>
+      <c r="BK3" s="1"/>
+      <c r="BL3" s="1"/>
+      <c r="BM3" s="1"/>
+      <c r="BN3" s="1"/>
+      <c r="BO3" s="1"/>
+      <c r="BP3" s="1"/>
+      <c r="BQ3" s="1"/>
+      <c r="BR3" s="1"/>
+      <c r="BS3" s="1"/>
+      <c r="BT3" s="1"/>
+      <c r="BU3" s="1"/>
+      <c r="BV3" s="1"/>
+      <c r="BW3" s="1"/>
+      <c r="BX3" s="1"/>
+      <c r="BY3" s="1"/>
+      <c r="BZ3" s="1"/>
+      <c r="CA3" s="1"/>
+      <c r="CB3" s="1"/>
+      <c r="CC3" s="1"/>
+      <c r="CD3" s="1"/>
+      <c r="CE3" s="1"/>
     </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="10" t="n">
+      <c r="D4" s="10">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10">
         <v>1</v>
       </c>
       <c r="F4" s="11"/>
@@ -1239,16 +1198,16 @@
       <c r="CD4" s="11"/>
       <c r="CE4" s="11"/>
     </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="14" t="n">
+      <c r="D5" s="14">
+        <v>1</v>
+      </c>
+      <c r="E5" s="14">
         <v>1</v>
       </c>
       <c r="F5" s="15"/>
@@ -1330,7 +1289,7 @@
       <c r="CD5" s="15"/>
       <c r="CE5" s="15"/>
     </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="8" t="s">
         <v>17</v>
@@ -1340,10 +1299,10 @@
       </c>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
-      <c r="F6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="10" t="n">
+      <c r="F6" s="10">
+        <v>1</v>
+      </c>
+      <c r="G6" s="10">
         <v>1</v>
       </c>
       <c r="H6" s="17"/>
@@ -1423,16 +1382,16 @@
       <c r="CD6" s="17"/>
       <c r="CE6" s="17"/>
     </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="13"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
-      <c r="F7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="14" t="n">
+      <c r="F7" s="14">
+        <v>1</v>
+      </c>
+      <c r="G7" s="14">
         <v>1</v>
       </c>
       <c r="H7" s="15"/>
@@ -1512,7 +1471,7 @@
       <c r="CD7" s="15"/>
       <c r="CE7" s="15"/>
     </row>
-    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>19</v>
       </c>
@@ -1526,10 +1485,10 @@
       <c r="E8" s="17"/>
       <c r="F8" s="17"/>
       <c r="G8" s="17"/>
-      <c r="H8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="10" t="n">
+      <c r="H8" s="10">
+        <v>1</v>
+      </c>
+      <c r="I8" s="10">
         <v>1</v>
       </c>
       <c r="J8" s="17"/>
@@ -1607,7 +1566,7 @@
       <c r="CD8" s="17"/>
       <c r="CE8" s="17"/>
     </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
       <c r="C9" s="13"/>
@@ -1615,10 +1574,10 @@
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
-      <c r="H9" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="14" t="n">
+      <c r="H9" s="14">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14">
         <v>1</v>
       </c>
       <c r="J9" s="15"/>
@@ -1696,7 +1655,7 @@
       <c r="CD9" s="15"/>
       <c r="CE9" s="15"/>
     </row>
-    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>19</v>
       </c>
@@ -1712,10 +1671,10 @@
       <c r="G10" s="17"/>
       <c r="H10" s="17"/>
       <c r="I10" s="17"/>
-      <c r="J10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="10" t="n">
+      <c r="J10" s="10">
+        <v>1</v>
+      </c>
+      <c r="K10" s="10">
         <v>1</v>
       </c>
       <c r="L10" s="17"/>
@@ -1791,7 +1750,7 @@
       <c r="CD10" s="17"/>
       <c r="CE10" s="17"/>
     </row>
-    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
       <c r="C11" s="13"/>
@@ -1801,10 +1760,10 @@
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
       <c r="I11" s="15"/>
-      <c r="J11" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="14" t="n">
+      <c r="J11" s="14">
+        <v>1</v>
+      </c>
+      <c r="K11" s="14">
         <v>1</v>
       </c>
       <c r="L11" s="15"/>
@@ -1880,7 +1839,7 @@
       <c r="CD11" s="15"/>
       <c r="CE11" s="15"/>
     </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>23</v>
       </c>
@@ -1898,16 +1857,16 @@
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
-      <c r="L12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" s="10" t="n">
+      <c r="L12" s="10">
+        <v>1</v>
+      </c>
+      <c r="M12" s="10">
+        <v>1</v>
+      </c>
+      <c r="N12" s="10">
+        <v>1</v>
+      </c>
+      <c r="O12" s="10">
         <v>1</v>
       </c>
       <c r="P12" s="17"/>
@@ -1979,7 +1938,7 @@
       <c r="CD12" s="17"/>
       <c r="CE12" s="17"/>
     </row>
-    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="12"/>
       <c r="C13" s="13"/>
@@ -1991,16 +1950,16 @@
       <c r="I13" s="15"/>
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
-      <c r="L13" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" s="14" t="n">
+      <c r="L13" s="14">
+        <v>1</v>
+      </c>
+      <c r="M13" s="14">
+        <v>1</v>
+      </c>
+      <c r="N13" s="14">
+        <v>1</v>
+      </c>
+      <c r="O13" s="14">
         <v>1</v>
       </c>
       <c r="P13" s="15"/>
@@ -2072,7 +2031,7 @@
       <c r="CD13" s="15"/>
       <c r="CE13" s="15"/>
     </row>
-    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>23</v>
       </c>
@@ -2094,10 +2053,10 @@
       <c r="M14" s="17"/>
       <c r="N14" s="17"/>
       <c r="O14" s="17"/>
-      <c r="P14" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="10" t="n">
+      <c r="P14" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="10">
         <v>1</v>
       </c>
       <c r="R14" s="17"/>
@@ -2167,7 +2126,7 @@
       <c r="CD14" s="17"/>
       <c r="CE14" s="17"/>
     </row>
-    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="12"/>
       <c r="C15" s="13"/>
@@ -2183,10 +2142,10 @@
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
-      <c r="P15" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="14" t="n">
+      <c r="P15" s="14">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="14">
         <v>1</v>
       </c>
       <c r="R15" s="15"/>
@@ -2256,7 +2215,7 @@
       <c r="CD15" s="15"/>
       <c r="CE15" s="15"/>
     </row>
-    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>23</v>
       </c>
@@ -2280,10 +2239,10 @@
       <c r="O16" s="17"/>
       <c r="P16" s="17"/>
       <c r="Q16" s="17"/>
-      <c r="R16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" s="10" t="n">
+      <c r="R16" s="10">
+        <v>1</v>
+      </c>
+      <c r="S16" s="10">
         <v>1</v>
       </c>
       <c r="T16" s="17"/>
@@ -2351,7 +2310,7 @@
       <c r="CD16" s="17"/>
       <c r="CE16" s="17"/>
     </row>
-    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="12"/>
       <c r="C17" s="13"/>
@@ -2369,10 +2328,10 @@
       <c r="O17" s="15"/>
       <c r="P17" s="15"/>
       <c r="Q17" s="15"/>
-      <c r="R17" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" s="14" t="n">
+      <c r="R17" s="14">
+        <v>1</v>
+      </c>
+      <c r="S17" s="14">
         <v>1</v>
       </c>
       <c r="T17" s="15"/>
@@ -2440,7 +2399,7 @@
       <c r="CD17" s="15"/>
       <c r="CE17" s="15"/>
     </row>
-    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>19</v>
       </c>
@@ -2466,10 +2425,10 @@
       <c r="Q18" s="17"/>
       <c r="R18" s="17"/>
       <c r="S18" s="17"/>
-      <c r="T18" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" s="10" t="n">
+      <c r="T18" s="10">
+        <v>1</v>
+      </c>
+      <c r="U18" s="10">
         <v>1</v>
       </c>
       <c r="V18" s="17"/>
@@ -2535,7 +2494,7 @@
       <c r="CD18" s="17"/>
       <c r="CE18" s="17"/>
     </row>
-    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
       <c r="C19" s="13"/>
@@ -2555,10 +2514,10 @@
       <c r="Q19" s="15"/>
       <c r="R19" s="15"/>
       <c r="S19" s="15"/>
-      <c r="T19" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" s="14" t="n">
+      <c r="T19" s="14">
+        <v>1</v>
+      </c>
+      <c r="U19" s="14">
         <v>1</v>
       </c>
       <c r="V19" s="15"/>
@@ -2624,7 +2583,7 @@
       <c r="CD19" s="15"/>
       <c r="CE19" s="15"/>
     </row>
-    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>23</v>
       </c>
@@ -2652,10 +2611,10 @@
       <c r="S20" s="17"/>
       <c r="T20" s="17"/>
       <c r="U20" s="17"/>
-      <c r="V20" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W20" s="10" t="n">
+      <c r="V20" s="10">
+        <v>1</v>
+      </c>
+      <c r="W20" s="10">
         <v>1</v>
       </c>
       <c r="X20" s="17"/>
@@ -2719,7 +2678,7 @@
       <c r="CD20" s="17"/>
       <c r="CE20" s="17"/>
     </row>
-    <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="13"/>
@@ -2741,10 +2700,10 @@
       <c r="S21" s="15"/>
       <c r="T21" s="15"/>
       <c r="U21" s="15"/>
-      <c r="V21" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="W21" s="14" t="n">
+      <c r="V21" s="14">
+        <v>1</v>
+      </c>
+      <c r="W21" s="14">
         <v>1</v>
       </c>
       <c r="X21" s="15"/>
@@ -2808,7 +2767,7 @@
       <c r="CD21" s="15"/>
       <c r="CE21" s="15"/>
     </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>23</v>
       </c>
@@ -2838,10 +2797,10 @@
       <c r="U22" s="17"/>
       <c r="V22" s="17"/>
       <c r="W22" s="17"/>
-      <c r="X22" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y22" s="10" t="n">
+      <c r="X22" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="10">
         <v>1</v>
       </c>
       <c r="Z22" s="17"/>
@@ -2903,7 +2862,7 @@
       <c r="CD22" s="17"/>
       <c r="CE22" s="17"/>
     </row>
-    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>
       <c r="B23" s="12"/>
       <c r="C23" s="13"/>
@@ -2988,7 +2947,7 @@
       <c r="CD23" s="15"/>
       <c r="CE23" s="15"/>
     </row>
-    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>23</v>
       </c>
@@ -3020,10 +2979,10 @@
       <c r="W24" s="17"/>
       <c r="X24" s="17"/>
       <c r="Y24" s="17"/>
-      <c r="Z24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA24" s="10" t="n">
+      <c r="Z24" s="10">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="10">
         <v>1</v>
       </c>
       <c r="AB24" s="17"/>
@@ -3083,7 +3042,7 @@
       <c r="CD24" s="17"/>
       <c r="CE24" s="17"/>
     </row>
-    <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="13"/>
@@ -3107,19 +3066,19 @@
       <c r="U25" s="15"/>
       <c r="V25" s="15"/>
       <c r="W25" s="15"/>
-      <c r="X25" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z25" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA25" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB25" s="14" t="n">
+      <c r="X25" s="14">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="14">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="14">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="14">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="14">
         <v>1</v>
       </c>
       <c r="AC25" s="15"/>
@@ -3178,7 +3137,7 @@
       <c r="CD25" s="15"/>
       <c r="CE25" s="15"/>
     </row>
-    <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>32</v>
       </c>
@@ -3212,10 +3171,10 @@
       <c r="Y26" s="17"/>
       <c r="Z26" s="17"/>
       <c r="AA26" s="17"/>
-      <c r="AB26" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC26" s="10" t="n">
+      <c r="AB26" s="10">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="10">
         <v>1</v>
       </c>
       <c r="AD26" s="17"/>
@@ -3273,7 +3232,7 @@
       <c r="CD26" s="17"/>
       <c r="CE26" s="17"/>
     </row>
-    <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
       <c r="C27" s="13"/>
@@ -3302,13 +3261,13 @@
       <c r="Z27" s="15"/>
       <c r="AA27" s="15"/>
       <c r="AB27" s="15"/>
-      <c r="AC27" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD27" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE27" s="14" t="n">
+      <c r="AC27" s="14">
+        <v>1</v>
+      </c>
+      <c r="AD27" s="14">
+        <v>1</v>
+      </c>
+      <c r="AE27" s="14">
         <v>1</v>
       </c>
       <c r="AF27" s="15"/>
@@ -3364,7 +3323,7 @@
       <c r="CD27" s="15"/>
       <c r="CE27" s="15"/>
     </row>
-    <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>32</v>
       </c>
@@ -3400,10 +3359,10 @@
       <c r="AA28" s="17"/>
       <c r="AB28" s="17"/>
       <c r="AC28" s="17"/>
-      <c r="AD28" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE28" s="10" t="n">
+      <c r="AD28" s="10">
+        <v>1</v>
+      </c>
+      <c r="AE28" s="10">
         <v>1</v>
       </c>
       <c r="AF28" s="17"/>
@@ -3459,7 +3418,7 @@
       <c r="CD28" s="17"/>
       <c r="CE28" s="17"/>
     </row>
-    <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="12"/>
       <c r="B29" s="12"/>
       <c r="C29" s="13"/>
@@ -3491,10 +3450,10 @@
       <c r="AC29" s="15"/>
       <c r="AD29" s="15"/>
       <c r="AE29" s="15"/>
-      <c r="AF29" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG29" s="14" t="n">
+      <c r="AF29" s="14">
+        <v>1</v>
+      </c>
+      <c r="AG29" s="14">
         <v>1</v>
       </c>
       <c r="AH29" s="15"/>
@@ -3548,7 +3507,7 @@
       <c r="CD29" s="15"/>
       <c r="CE29" s="15"/>
     </row>
-    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>32</v>
       </c>
@@ -3586,10 +3545,10 @@
       <c r="AC30" s="17"/>
       <c r="AD30" s="17"/>
       <c r="AE30" s="17"/>
-      <c r="AF30" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG30" s="10" t="n">
+      <c r="AF30" s="10">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="10">
         <v>1</v>
       </c>
       <c r="AH30" s="17"/>
@@ -3643,7 +3602,7 @@
       <c r="CD30" s="17"/>
       <c r="CE30" s="17"/>
     </row>
-    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="12"/>
       <c r="B31" s="12"/>
       <c r="C31" s="13"/>
@@ -3677,7 +3636,7 @@
       <c r="AE31" s="15"/>
       <c r="AF31" s="15"/>
       <c r="AG31" s="15"/>
-      <c r="AH31" s="14" t="n">
+      <c r="AH31" s="14">
         <v>1</v>
       </c>
       <c r="AI31" s="15"/>
@@ -3730,7 +3689,7 @@
       <c r="CD31" s="15"/>
       <c r="CE31" s="15"/>
     </row>
-    <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>32</v>
       </c>
@@ -3770,10 +3729,10 @@
       <c r="AE32" s="17"/>
       <c r="AF32" s="17"/>
       <c r="AG32" s="17"/>
-      <c r="AH32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI32" s="10" t="n">
+      <c r="AH32" s="10">
+        <v>1</v>
+      </c>
+      <c r="AI32" s="10">
         <v>1</v>
       </c>
       <c r="AJ32" s="17"/>
@@ -3825,7 +3784,7 @@
       <c r="CD32" s="17"/>
       <c r="CE32" s="17"/>
     </row>
-    <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="12"/>
       <c r="B33" s="12"/>
       <c r="C33" s="13"/>
@@ -3860,7 +3819,7 @@
       <c r="AF33" s="15"/>
       <c r="AG33" s="15"/>
       <c r="AH33" s="15"/>
-      <c r="AI33" s="14" t="n">
+      <c r="AI33" s="14">
         <v>1</v>
       </c>
       <c r="AJ33" s="15"/>
@@ -3912,7 +3871,7 @@
       <c r="CD33" s="15"/>
       <c r="CE33" s="15"/>
     </row>
-    <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>38</v>
       </c>
@@ -3954,10 +3913,10 @@
       <c r="AG34" s="17"/>
       <c r="AH34" s="17"/>
       <c r="AI34" s="17"/>
-      <c r="AJ34" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK34" s="10" t="n">
+      <c r="AJ34" s="10">
+        <v>1</v>
+      </c>
+      <c r="AK34" s="10">
         <v>1</v>
       </c>
       <c r="AL34" s="17"/>
@@ -4007,7 +3966,7 @@
       <c r="CD34" s="17"/>
       <c r="CE34" s="17"/>
     </row>
-    <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="12"/>
       <c r="B35" s="12"/>
       <c r="C35" s="13"/>
@@ -4043,7 +4002,7 @@
       <c r="AG35" s="15"/>
       <c r="AH35" s="15"/>
       <c r="AI35" s="15"/>
-      <c r="AJ35" s="14" t="n">
+      <c r="AJ35" s="14">
         <v>1</v>
       </c>
       <c r="AK35" s="15"/>
@@ -4094,7 +4053,7 @@
       <c r="CD35" s="15"/>
       <c r="CE35" s="15"/>
     </row>
-    <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>38</v>
       </c>
@@ -4138,22 +4097,22 @@
       <c r="AI36" s="17"/>
       <c r="AJ36" s="17"/>
       <c r="AK36" s="17"/>
-      <c r="AL36" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM36" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN36" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO36" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP36" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ36" s="10" t="n">
+      <c r="AL36" s="10">
+        <v>1</v>
+      </c>
+      <c r="AM36" s="10">
+        <v>1</v>
+      </c>
+      <c r="AN36" s="10">
+        <v>1</v>
+      </c>
+      <c r="AO36" s="10">
+        <v>1</v>
+      </c>
+      <c r="AP36" s="10">
+        <v>1</v>
+      </c>
+      <c r="AQ36" s="10">
         <v>1</v>
       </c>
       <c r="AR36" s="17"/>
@@ -4197,7 +4156,7 @@
       <c r="CD36" s="17"/>
       <c r="CE36" s="17"/>
     </row>
-    <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="13"/>
@@ -4234,25 +4193,25 @@
       <c r="AH37" s="15"/>
       <c r="AI37" s="15"/>
       <c r="AJ37" s="15"/>
-      <c r="AK37" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL37" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM37" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN37" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO37" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP37" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ37" s="14" t="n">
+      <c r="AK37" s="14">
+        <v>1</v>
+      </c>
+      <c r="AL37" s="14">
+        <v>1</v>
+      </c>
+      <c r="AM37" s="14">
+        <v>1</v>
+      </c>
+      <c r="AN37" s="14">
+        <v>1</v>
+      </c>
+      <c r="AO37" s="14">
+        <v>1</v>
+      </c>
+      <c r="AP37" s="14">
+        <v>1</v>
+      </c>
+      <c r="AQ37" s="14">
         <v>1</v>
       </c>
       <c r="AR37" s="15"/>
@@ -4296,7 +4255,7 @@
       <c r="CD37" s="15"/>
       <c r="CE37" s="15"/>
     </row>
-    <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>38</v>
       </c>
@@ -4346,10 +4305,10 @@
       <c r="AO38" s="17"/>
       <c r="AP38" s="17"/>
       <c r="AQ38" s="17"/>
-      <c r="AR38" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS38" s="10" t="n">
+      <c r="AR38" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS38" s="10">
         <v>1</v>
       </c>
       <c r="AT38" s="17"/>
@@ -4391,7 +4350,7 @@
       <c r="CD38" s="17"/>
       <c r="CE38" s="17"/>
     </row>
-    <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12"/>
       <c r="B39" s="12"/>
       <c r="C39" s="13"/>
@@ -4435,10 +4394,10 @@
       <c r="AO39" s="15"/>
       <c r="AP39" s="15"/>
       <c r="AQ39" s="15"/>
-      <c r="AR39" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS39" s="14" t="n">
+      <c r="AR39" s="14">
+        <v>1</v>
+      </c>
+      <c r="AS39" s="14">
         <v>1</v>
       </c>
       <c r="AT39" s="15"/>
@@ -4480,7 +4439,7 @@
       <c r="CD39" s="15"/>
       <c r="CE39" s="15"/>
     </row>
-    <row r="40" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
         <v>38</v>
       </c>
@@ -4532,16 +4491,16 @@
       <c r="AQ40" s="17"/>
       <c r="AR40" s="17"/>
       <c r="AS40" s="17"/>
-      <c r="AT40" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU40" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV40" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW40" s="10" t="n">
+      <c r="AT40" s="10">
+        <v>1</v>
+      </c>
+      <c r="AU40" s="10">
+        <v>1</v>
+      </c>
+      <c r="AV40" s="10">
+        <v>1</v>
+      </c>
+      <c r="AW40" s="10">
         <v>1</v>
       </c>
       <c r="AX40" s="17"/>
@@ -4579,7 +4538,7 @@
       <c r="CD40" s="17"/>
       <c r="CE40" s="17"/>
     </row>
-    <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="12"/>
       <c r="B41" s="12"/>
       <c r="C41" s="13"/>
@@ -4629,10 +4588,10 @@
       <c r="AU41" s="15"/>
       <c r="AV41" s="15"/>
       <c r="AW41" s="15"/>
-      <c r="AX41" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY41" s="14" t="n">
+      <c r="AX41" s="14">
+        <v>1</v>
+      </c>
+      <c r="AY41" s="14">
         <v>1</v>
       </c>
       <c r="AZ41" s="15"/>
@@ -4668,7 +4627,7 @@
       <c r="CD41" s="15"/>
       <c r="CE41" s="15"/>
     </row>
-    <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>38</v>
       </c>
@@ -4724,10 +4683,10 @@
       <c r="AU42" s="17"/>
       <c r="AV42" s="17"/>
       <c r="AW42" s="17"/>
-      <c r="AX42" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY42" s="10" t="n">
+      <c r="AX42" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY42" s="10">
         <v>1</v>
       </c>
       <c r="AZ42" s="17"/>
@@ -4763,7 +4722,7 @@
       <c r="CD42" s="17"/>
       <c r="CE42" s="17"/>
     </row>
-    <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12"/>
       <c r="B43" s="12"/>
       <c r="C43" s="13"/>
@@ -4809,16 +4768,16 @@
       <c r="AQ43" s="15"/>
       <c r="AR43" s="15"/>
       <c r="AS43" s="15"/>
-      <c r="AT43" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU43" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV43" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW43" s="14" t="n">
+      <c r="AT43" s="14">
+        <v>1</v>
+      </c>
+      <c r="AU43" s="14">
+        <v>1</v>
+      </c>
+      <c r="AV43" s="14">
+        <v>1</v>
+      </c>
+      <c r="AW43" s="14">
         <v>1</v>
       </c>
       <c r="AX43" s="15"/>
@@ -4856,7 +4815,7 @@
       <c r="CD43" s="15"/>
       <c r="CE43" s="15"/>
     </row>
-    <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>38</v>
       </c>
@@ -4914,16 +4873,16 @@
       <c r="AW44" s="17"/>
       <c r="AX44" s="17"/>
       <c r="AY44" s="17"/>
-      <c r="AZ44" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA44" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB44" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC44" s="10" t="n">
+      <c r="AZ44" s="10">
+        <v>1</v>
+      </c>
+      <c r="BA44" s="10">
+        <v>1</v>
+      </c>
+      <c r="BB44" s="10">
+        <v>1</v>
+      </c>
+      <c r="BC44" s="10">
         <v>1</v>
       </c>
       <c r="BD44" s="17"/>
@@ -4955,7 +4914,7 @@
       <c r="CD44" s="17"/>
       <c r="CE44" s="17"/>
     </row>
-    <row r="45" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="12"/>
       <c r="B45" s="12"/>
       <c r="C45" s="13"/>
@@ -5009,22 +4968,22 @@
       <c r="AY45" s="15"/>
       <c r="AZ45" s="15"/>
       <c r="BA45" s="15"/>
-      <c r="BB45" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC45" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD45" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE45" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF45" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG45" s="14" t="n">
+      <c r="BB45" s="14">
+        <v>1</v>
+      </c>
+      <c r="BC45" s="14">
+        <v>1</v>
+      </c>
+      <c r="BD45" s="14">
+        <v>1</v>
+      </c>
+      <c r="BE45" s="14">
+        <v>1</v>
+      </c>
+      <c r="BF45" s="14">
+        <v>1</v>
+      </c>
+      <c r="BG45" s="14">
         <v>1</v>
       </c>
       <c r="BH45" s="15"/>
@@ -5052,7 +5011,7 @@
       <c r="CD45" s="15"/>
       <c r="CE45" s="15"/>
     </row>
-    <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>38</v>
       </c>
@@ -5114,16 +5073,16 @@
       <c r="BA46" s="17"/>
       <c r="BB46" s="17"/>
       <c r="BC46" s="17"/>
-      <c r="BD46" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE46" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF46" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG46" s="10" t="n">
+      <c r="BD46" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE46" s="10">
+        <v>1</v>
+      </c>
+      <c r="BF46" s="10">
+        <v>1</v>
+      </c>
+      <c r="BG46" s="10">
         <v>1</v>
       </c>
       <c r="BH46" s="17"/>
@@ -5151,7 +5110,7 @@
       <c r="CD46" s="17"/>
       <c r="CE46" s="17"/>
     </row>
-    <row r="47" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="12"/>
       <c r="B47" s="12"/>
       <c r="C47" s="13"/>
@@ -5203,10 +5162,10 @@
       <c r="AW47" s="15"/>
       <c r="AX47" s="15"/>
       <c r="AY47" s="15"/>
-      <c r="AZ47" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA47" s="14" t="n">
+      <c r="AZ47" s="14">
+        <v>1</v>
+      </c>
+      <c r="BA47" s="14">
         <v>1</v>
       </c>
       <c r="BB47" s="15"/>
@@ -5215,28 +5174,28 @@
       <c r="BE47" s="15"/>
       <c r="BF47" s="15"/>
       <c r="BG47" s="15"/>
-      <c r="BH47" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI47" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ47" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK47" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL47" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM47" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN47" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO47" s="14" t="n">
+      <c r="BH47" s="14">
+        <v>1</v>
+      </c>
+      <c r="BI47" s="14">
+        <v>1</v>
+      </c>
+      <c r="BJ47" s="14">
+        <v>1</v>
+      </c>
+      <c r="BK47" s="14">
+        <v>1</v>
+      </c>
+      <c r="BL47" s="14">
+        <v>1</v>
+      </c>
+      <c r="BM47" s="14">
+        <v>1</v>
+      </c>
+      <c r="BN47" s="14">
+        <v>1</v>
+      </c>
+      <c r="BO47" s="14">
         <v>1</v>
       </c>
       <c r="BP47" s="15"/>
@@ -5256,7 +5215,7 @@
       <c r="CD47" s="15"/>
       <c r="CE47" s="15"/>
     </row>
-    <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>47</v>
       </c>
@@ -5322,16 +5281,16 @@
       <c r="BE48" s="17"/>
       <c r="BF48" s="17"/>
       <c r="BG48" s="17"/>
-      <c r="BH48" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI48" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ48" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK48" s="10" t="n">
+      <c r="BH48" s="10">
+        <v>1</v>
+      </c>
+      <c r="BI48" s="10">
+        <v>1</v>
+      </c>
+      <c r="BJ48" s="10">
+        <v>1</v>
+      </c>
+      <c r="BK48" s="10">
         <v>1</v>
       </c>
       <c r="BL48" s="17"/>
@@ -5355,7 +5314,7 @@
       <c r="CD48" s="17"/>
       <c r="CE48" s="17"/>
     </row>
-    <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="12"/>
       <c r="B49" s="12"/>
       <c r="C49" s="13"/>
@@ -5440,7 +5399,7 @@
       <c r="CD49" s="15"/>
       <c r="CE49" s="15"/>
     </row>
-    <row r="50" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>47</v>
       </c>
@@ -5510,16 +5469,16 @@
       <c r="BI50" s="17"/>
       <c r="BJ50" s="17"/>
       <c r="BK50" s="17"/>
-      <c r="BL50" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM50" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN50" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO50" s="10" t="n">
+      <c r="BL50" s="10">
+        <v>1</v>
+      </c>
+      <c r="BM50" s="10">
+        <v>1</v>
+      </c>
+      <c r="BN50" s="10">
+        <v>1</v>
+      </c>
+      <c r="BO50" s="10">
         <v>1</v>
       </c>
       <c r="BP50" s="17"/>
@@ -5539,7 +5498,7 @@
       <c r="CD50" s="17"/>
       <c r="CE50" s="17"/>
     </row>
-    <row r="51" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="12"/>
       <c r="B51" s="12"/>
       <c r="C51" s="13"/>
@@ -5624,7 +5583,7 @@
       <c r="CD51" s="15"/>
       <c r="CE51" s="15"/>
     </row>
-    <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>51</v>
       </c>
@@ -5698,16 +5657,16 @@
       <c r="BM52" s="17"/>
       <c r="BN52" s="17"/>
       <c r="BO52" s="17"/>
-      <c r="BP52" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ52" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR52" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS52" s="10" t="n">
+      <c r="BP52" s="10">
+        <v>1</v>
+      </c>
+      <c r="BQ52" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR52" s="10">
+        <v>1</v>
+      </c>
+      <c r="BS52" s="10">
         <v>1</v>
       </c>
       <c r="BT52" s="17"/>
@@ -5723,7 +5682,7 @@
       <c r="CD52" s="17"/>
       <c r="CE52" s="17"/>
     </row>
-    <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12"/>
       <c r="B53" s="12"/>
       <c r="C53" s="13"/>
@@ -5791,10 +5750,18 @@
       <c r="BM53" s="15"/>
       <c r="BN53" s="15"/>
       <c r="BO53" s="15"/>
-      <c r="BP53" s="15"/>
-      <c r="BQ53" s="15"/>
-      <c r="BR53" s="15"/>
-      <c r="BS53" s="15"/>
+      <c r="BP53" s="14">
+        <v>1</v>
+      </c>
+      <c r="BQ53" s="14">
+        <v>1</v>
+      </c>
+      <c r="BR53" s="14">
+        <v>1</v>
+      </c>
+      <c r="BS53" s="14">
+        <v>1</v>
+      </c>
       <c r="BT53" s="15"/>
       <c r="BU53" s="15"/>
       <c r="BV53" s="15"/>
@@ -5808,7 +5775,7 @@
       <c r="CD53" s="15"/>
       <c r="CE53" s="15"/>
     </row>
-    <row r="54" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>54</v>
       </c>
@@ -5886,16 +5853,16 @@
       <c r="BQ54" s="17"/>
       <c r="BR54" s="17"/>
       <c r="BS54" s="17"/>
-      <c r="BT54" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU54" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV54" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BW54" s="10" t="n">
+      <c r="BT54" s="10">
+        <v>1</v>
+      </c>
+      <c r="BU54" s="10">
+        <v>1</v>
+      </c>
+      <c r="BV54" s="10">
+        <v>1</v>
+      </c>
+      <c r="BW54" s="10">
         <v>1</v>
       </c>
       <c r="BX54" s="17"/>
@@ -5907,7 +5874,7 @@
       <c r="CD54" s="17"/>
       <c r="CE54" s="17"/>
     </row>
-    <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="12"/>
       <c r="B55" s="12"/>
       <c r="C55" s="13"/>
@@ -5979,10 +5946,18 @@
       <c r="BQ55" s="15"/>
       <c r="BR55" s="15"/>
       <c r="BS55" s="15"/>
-      <c r="BT55" s="15"/>
-      <c r="BU55" s="15"/>
-      <c r="BV55" s="15"/>
-      <c r="BW55" s="15"/>
+      <c r="BT55" s="14">
+        <v>1</v>
+      </c>
+      <c r="BU55" s="14">
+        <v>1</v>
+      </c>
+      <c r="BV55" s="14">
+        <v>1</v>
+      </c>
+      <c r="BW55" s="14">
+        <v>1</v>
+      </c>
       <c r="BX55" s="15"/>
       <c r="BY55" s="15"/>
       <c r="BZ55" s="15"/>
@@ -5992,7 +5967,7 @@
       <c r="CD55" s="15"/>
       <c r="CE55" s="15"/>
     </row>
-    <row r="56" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>54</v>
       </c>
@@ -6074,16 +6049,16 @@
       <c r="BU56" s="17"/>
       <c r="BV56" s="17"/>
       <c r="BW56" s="17"/>
-      <c r="BX56" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY56" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BZ56" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CA56" s="10" t="n">
+      <c r="BX56" s="10">
+        <v>1</v>
+      </c>
+      <c r="BY56" s="10">
+        <v>1</v>
+      </c>
+      <c r="BZ56" s="10">
+        <v>1</v>
+      </c>
+      <c r="CA56" s="10">
         <v>1</v>
       </c>
       <c r="CB56" s="17"/>
@@ -6091,7 +6066,7 @@
       <c r="CD56" s="17"/>
       <c r="CE56" s="17"/>
     </row>
-    <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="12"/>
       <c r="B57" s="12"/>
       <c r="C57" s="13"/>
@@ -6167,16 +6142,24 @@
       <c r="BU57" s="15"/>
       <c r="BV57" s="15"/>
       <c r="BW57" s="15"/>
-      <c r="BX57" s="15"/>
-      <c r="BY57" s="15"/>
-      <c r="BZ57" s="15"/>
-      <c r="CA57" s="15"/>
+      <c r="BX57" s="14">
+        <v>1</v>
+      </c>
+      <c r="BY57" s="14">
+        <v>1</v>
+      </c>
+      <c r="BZ57" s="14">
+        <v>1</v>
+      </c>
+      <c r="CA57" s="14">
+        <v>1</v>
+      </c>
       <c r="CB57" s="15"/>
       <c r="CC57" s="15"/>
       <c r="CD57" s="15"/>
       <c r="CE57" s="15"/>
     </row>
-    <row r="58" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>54</v>
       </c>
@@ -6262,16 +6245,16 @@
       <c r="BY58" s="17"/>
       <c r="BZ58" s="17"/>
       <c r="CA58" s="17"/>
-      <c r="CB58" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CC58" s="10" t="n">
+      <c r="CB58" s="10">
+        <v>1</v>
+      </c>
+      <c r="CC58" s="10">
         <v>1</v>
       </c>
       <c r="CD58" s="17"/>
       <c r="CE58" s="17"/>
     </row>
-    <row r="59" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="12"/>
       <c r="B59" s="12"/>
       <c r="C59" s="13"/>
@@ -6351,12 +6334,16 @@
       <c r="BY59" s="15"/>
       <c r="BZ59" s="15"/>
       <c r="CA59" s="15"/>
-      <c r="CB59" s="15"/>
-      <c r="CC59" s="15"/>
+      <c r="CB59" s="14">
+        <v>1</v>
+      </c>
+      <c r="CC59" s="14">
+        <v>1</v>
+      </c>
       <c r="CD59" s="15"/>
       <c r="CE59" s="15"/>
     </row>
-    <row r="60" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
         <v>54</v>
       </c>
@@ -6444,14 +6431,14 @@
       <c r="CA60" s="17"/>
       <c r="CB60" s="17"/>
       <c r="CC60" s="17"/>
-      <c r="CD60" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE60" s="10" t="n">
+      <c r="CD60" s="10">
+        <v>1</v>
+      </c>
+      <c r="CE60" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:83" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="12"/>
       <c r="B61" s="12"/>
       <c r="C61" s="13"/>
@@ -6533,10 +6520,14 @@
       <c r="CA61" s="15"/>
       <c r="CB61" s="15"/>
       <c r="CC61" s="15"/>
-      <c r="CD61" s="15"/>
-      <c r="CE61" s="15"/>
+      <c r="CD61" s="14">
+        <v>1</v>
+      </c>
+      <c r="CE61" s="14">
+        <v>1</v>
+      </c>
     </row>
-    <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
       <c r="C62" s="16"/>
@@ -6621,7 +6612,7 @@
       <c r="CD62" s="17"/>
       <c r="CE62" s="17"/>
     </row>
-    <row r="63" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="12"/>
       <c r="B63" s="12"/>
       <c r="C63" s="13"/>
@@ -6706,7 +6697,7 @@
       <c r="CD63" s="15"/>
       <c r="CE63" s="15"/>
     </row>
-    <row r="64" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
       <c r="C64" s="16"/>
@@ -6791,7 +6782,7 @@
       <c r="CD64" s="17"/>
       <c r="CE64" s="17"/>
     </row>
-    <row r="65" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="12"/>
       <c r="B65" s="12"/>
       <c r="C65" s="13"/>
@@ -6876,7 +6867,7 @@
       <c r="CD65" s="15"/>
       <c r="CE65" s="15"/>
     </row>
-    <row r="66" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="8"/>
       <c r="B66" s="8"/>
       <c r="C66" s="16"/>
@@ -6961,7 +6952,7 @@
       <c r="CD66" s="17"/>
       <c r="CE66" s="17"/>
     </row>
-    <row r="67" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="12"/>
       <c r="B67" s="12"/>
       <c r="C67" s="13"/>
@@ -7046,7 +7037,7 @@
       <c r="CD67" s="15"/>
       <c r="CE67" s="15"/>
     </row>
-    <row r="68" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>
       <c r="B68" s="8"/>
       <c r="C68" s="16"/>
@@ -7131,7 +7122,7 @@
       <c r="CD68" s="17"/>
       <c r="CE68" s="17"/>
     </row>
-    <row r="69" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="12"/>
       <c r="B69" s="12"/>
       <c r="C69" s="13"/>
@@ -7216,7 +7207,7 @@
       <c r="CD69" s="15"/>
       <c r="CE69" s="15"/>
     </row>
-    <row r="70" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="8"/>
       <c r="B70" s="8"/>
       <c r="C70" s="16"/>
@@ -7301,7 +7292,7 @@
       <c r="CD70" s="17"/>
       <c r="CE70" s="17"/>
     </row>
-    <row r="71" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="12"/>
       <c r="B71" s="12"/>
       <c r="C71" s="13"/>
@@ -7386,7 +7377,7 @@
       <c r="CD71" s="15"/>
       <c r="CE71" s="15"/>
     </row>
-    <row r="72" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="8"/>
       <c r="B72" s="8"/>
       <c r="C72" s="16"/>
@@ -7471,7 +7462,7 @@
       <c r="CD72" s="17"/>
       <c r="CE72" s="17"/>
     </row>
-    <row r="73" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="12"/>
       <c r="B73" s="12"/>
       <c r="C73" s="13"/>
@@ -7556,7 +7547,7 @@
       <c r="CD73" s="15"/>
       <c r="CE73" s="15"/>
     </row>
-    <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="8"/>
       <c r="B74" s="8"/>
       <c r="C74" s="16"/>
@@ -7641,7 +7632,7 @@
       <c r="CD74" s="17"/>
       <c r="CE74" s="17"/>
     </row>
-    <row r="75" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="12"/>
       <c r="B75" s="12"/>
       <c r="C75" s="13"/>
@@ -7726,7 +7717,7 @@
       <c r="CD75" s="15"/>
       <c r="CE75" s="15"/>
     </row>
-    <row r="76" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="8"/>
       <c r="B76" s="8"/>
       <c r="C76" s="16"/>
@@ -7811,7 +7802,7 @@
       <c r="CD76" s="17"/>
       <c r="CE76" s="17"/>
     </row>
-    <row r="77" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="12"/>
       <c r="B77" s="12"/>
       <c r="C77" s="13"/>
@@ -7896,7 +7887,7 @@
       <c r="CD77" s="15"/>
       <c r="CE77" s="15"/>
     </row>
-    <row r="78" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="8"/>
       <c r="B78" s="8"/>
       <c r="C78" s="16"/>
@@ -7981,7 +7972,7 @@
       <c r="CD78" s="17"/>
       <c r="CE78" s="17"/>
     </row>
-    <row r="79" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="12"/>
       <c r="B79" s="12"/>
       <c r="C79" s="13"/>
@@ -8066,7 +8057,7 @@
       <c r="CD79" s="15"/>
       <c r="CE79" s="15"/>
     </row>
-    <row r="80" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="8"/>
       <c r="B80" s="8"/>
       <c r="C80" s="16"/>
@@ -8151,7 +8142,7 @@
       <c r="CD80" s="17"/>
       <c r="CE80" s="17"/>
     </row>
-    <row r="81" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="12"/>
       <c r="B81" s="12"/>
       <c r="C81" s="13"/>
@@ -8236,7 +8227,7 @@
       <c r="CD81" s="15"/>
       <c r="CE81" s="15"/>
     </row>
-    <row r="82" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="82" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="8"/>
       <c r="B82" s="8"/>
       <c r="C82" s="16"/>
@@ -8321,7 +8312,7 @@
       <c r="CD82" s="17"/>
       <c r="CE82" s="17"/>
     </row>
-    <row r="83" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" spans="1:83" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="12"/>
       <c r="B83" s="12"/>
       <c r="C83" s="13"/>
@@ -8408,24 +8399,19 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="D3:CE3"/>
+    <mergeCell ref="AR1:AY1"/>
+    <mergeCell ref="AZ1:BG1"/>
+    <mergeCell ref="BH1:BO1"/>
+    <mergeCell ref="BP1:BW1"/>
+    <mergeCell ref="BX1:CE1"/>
     <mergeCell ref="D1:K1"/>
     <mergeCell ref="L1:S1"/>
     <mergeCell ref="T1:AA1"/>
     <mergeCell ref="AB1:AI1"/>
     <mergeCell ref="AJ1:AQ1"/>
-    <mergeCell ref="AR1:AY1"/>
-    <mergeCell ref="AZ1:BG1"/>
-    <mergeCell ref="BH1:BO1"/>
-    <mergeCell ref="BP1:BW1"/>
-    <mergeCell ref="BX1:CE1"/>
-    <mergeCell ref="D3:CE3"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>